--- a/Side Bar Files/GWD Data/Services.xlsx
+++ b/Side Bar Files/GWD Data/Services.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
   <si>
     <t>Sl. No</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>5 hrs</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Rotary cum DTH OB Drilling with Subsidy</t>
   </si>
 </sst>
 </file>
@@ -384,7 +390,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_7" displayName="Table_7" ref="A1:D20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_9" displayName="Table_9" ref="A1:D21">
   <tableColumns count="4">
     <tableColumn id="1" name="Sl. No"/>
     <tableColumn id="2" name="Item Name"/>
@@ -691,8 +697,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C56C4-C1B2-4CAD-A1DD-E57BE86AB9A6}">
-  <dimension ref="A1:D20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85C58BF9-EAC5-4B95-9559-F1A4A2A0B9A7}">
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:4" ht="12.75">
@@ -974,6 +980,21 @@
       </c>
       <c r="D20" s="5">
         <v>7490</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="12.75">
+      <c r="A21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="5">
+        <f>D19/2</f>
+        <v>992.50</v>
       </c>
     </row>
   </sheetData>

--- a/Side Bar Files/GWD Data/Services.xlsx
+++ b/Side Bar Files/GWD Data/Services.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="62">
   <si>
     <t>Sl. No</t>
   </si>
@@ -165,6 +165,42 @@
   </si>
   <si>
     <t>Rotary cum DTH OB Drilling with Subsidy</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>150mm (6") Borewell Drilling with Subsidy</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>150mm (6") Tubewell Drilling with Subsidy</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Tubewell Drilling 200mm (8") with Subsidy</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Water Quality Testing</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Water Quality Testing Including Bacteriology</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Slotting charge for 3m pipe, net, rope, pipe fittings and sundries for Filter Point Well Construction</t>
   </si>
 </sst>
 </file>
@@ -223,25 +259,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -271,11 +293,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -390,7 +412,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_9" displayName="Table_9" ref="A1:D21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_8" displayName="Table_8" ref="A1:D27">
   <tableColumns count="4">
     <tableColumn id="1" name="Sl. No"/>
     <tableColumn id="2" name="Item Name"/>
@@ -697,8 +719,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85C58BF9-EAC5-4B95-9559-F1A4A2A0B9A7}">
-  <dimension ref="A1:D21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20993962-A010-403D-B801-07C1CCACBAA6}">
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:4" ht="12.75">
@@ -995,6 +1017,93 @@
       <c r="D21" s="5">
         <f>D19/2</f>
         <v>992.50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="12.75">
+      <c r="A22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="5">
+        <f>D7/2</f>
+        <v>332.50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="12.75">
+      <c r="A23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="5">
+        <f>D8/2</f>
+        <v>1157.50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="12.75">
+      <c r="A24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="5">
+        <f>D9/2</f>
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="12.75">
+      <c r="A25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="12.75">
+      <c r="A26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="5">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="12.75">
+      <c r="A27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1200</v>
       </c>
     </row>
   </sheetData>

--- a/Side Bar Files/GWD Data/Services.xlsx
+++ b/Side Bar Files/GWD Data/Services.xlsx
@@ -719,7 +719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20993962-A010-403D-B801-07C1CCACBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD4E3D01-AD67-4A3B-8484-EF537DF3BAA6}">
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Services.xlsx
+++ b/Side Bar Files/GWD Data/Services.xlsx
@@ -719,7 +719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD4E3D01-AD67-4A3B-8484-EF537DF3BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA36D8A-99FF-4906-84BB-8BA1EFA8BAA6}">
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
